--- a/docs/samples/written/テンプレ.xlsx
+++ b/docs/samples/written/テンプレ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\サンゴ申込書最新\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd35f0bba0eb985b/デスクトップ/VEXUM/プラージュ様/-OCR-main/-OCR-main/docs/samples/written/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F019FE3E-5A0B-4EAC-9E9D-3FDCC8F2D39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{F019FE3E-5A0B-4EAC-9E9D-3FDCC8F2D39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{039099D8-98D8-4338-8D1E-591EAAF6B751}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D7B9D4FA-DB95-4859-9995-F738ACF57FA8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D7B9D4FA-DB95-4859-9995-F738ACF57FA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>【訪問理美容サービス　申込書】</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>※ご希望の施術内容に〇印をつけてください。</t>
-  </si>
-  <si>
-    <t>施設側</t>
   </si>
   <si>
     <t>訪問側</t>
@@ -243,6 +240,20 @@
     <t>✓</t>
     <phoneticPr fontId="9"/>
   </si>
+  <si>
+    <t>施設側</t>
+    <rPh sb="0" eb="2">
+      <t>シセツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>案内担当</t>
+    <rPh sb="0" eb="4">
+      <t>アンナイタントウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
@@ -253,7 +264,7 @@
     <numFmt numFmtId="176" formatCode="[$¥-411]#,##0"/>
     <numFmt numFmtId="177" formatCode="&quot;¥&quot;#,##0_);[Red]\(&quot;¥&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -475,7 +486,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -499,19 +510,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1061,7 +1059,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1091,9 +1089,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1103,19 +1098,22 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="18" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1124,22 +1122,19 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1148,91 +1143,170 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="24" fillId="5" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="24" fillId="5" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1242,103 +1316,24 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1359,9 +1354,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1399,7 +1394,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1505,7 +1500,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1647,7 +1642,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1659,23 +1654,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y57"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="7.625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="7.58203125" style="4" customWidth="1"/>
     <col min="3" max="5" width="11" style="4"/>
-    <col min="6" max="6" width="8.875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="4" customWidth="1"/>
     <col min="7" max="14" width="10" style="4" customWidth="1"/>
     <col min="15" max="15" width="11" style="4"/>
-    <col min="16" max="18" width="8.875" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.375" style="4" customWidth="1"/>
+    <col min="16" max="18" width="8.83203125" style="4" customWidth="1"/>
+    <col min="19" max="19" width="10.33203125" style="4" customWidth="1"/>
     <col min="20" max="20" width="11" style="4"/>
-    <col min="21" max="21" width="12.375" style="4" customWidth="1"/>
+    <col min="21" max="21" width="12.33203125" style="4" customWidth="1"/>
     <col min="22" max="22" width="12.5" style="4" customWidth="1"/>
     <col min="23" max="16384" width="11" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="32.25">
+    <row r="1" spans="1:25" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1701,7 +1696,7 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:25" ht="14.25">
+    <row r="2" spans="1:25" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -1723,7 +1718,7 @@
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
     </row>
-    <row r="3" spans="1:25" ht="19.5">
+    <row r="3" spans="1:25" ht="20" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="6"/>
       <c r="B3" s="6" t="s">
         <v>1</v>
@@ -1743,15 +1738,15 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="Q3" s="7"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="81"/>
-      <c r="U3" s="82" t="s">
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="V3" s="82"/>
-    </row>
-    <row r="4" spans="1:25" ht="19.5">
+      <c r="V3" s="78"/>
+    </row>
+    <row r="4" spans="1:25" ht="23" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
         <v>4</v>
@@ -1774,16 +1769,19 @@
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
       <c r="U4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="V4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="W4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="V4" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="18">
+    </row>
+    <row r="5" spans="1:25" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -1802,13 +1800,14 @@
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
-      <c r="U5" s="83"/>
-      <c r="V5" s="86"/>
-    </row>
-    <row r="6" spans="1:25" ht="18">
+      <c r="U5" s="79"/>
+      <c r="V5" s="82"/>
+      <c r="W5" s="82"/>
+    </row>
+    <row r="6" spans="1:25" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -1820,13 +1819,14 @@
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
-      <c r="U6" s="84"/>
-      <c r="V6" s="87"/>
-    </row>
-    <row r="7" spans="1:25" ht="18">
+      <c r="U6" s="80"/>
+      <c r="V6" s="83"/>
+      <c r="W6" s="83"/>
+    </row>
+    <row r="7" spans="1:25" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -1845,16 +1845,16 @@
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
-      <c r="U7" s="84"/>
-      <c r="V7" s="87"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
+      <c r="U7" s="80"/>
+      <c r="V7" s="83"/>
+      <c r="W7" s="83"/>
+      <c r="X7" s="11"/>
       <c r="Y7" s="5"/>
     </row>
-    <row r="8" spans="1:25" ht="18">
+    <row r="8" spans="1:25" ht="18.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -1873,16 +1873,16 @@
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
-      <c r="U8" s="85"/>
-      <c r="V8" s="88"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
+      <c r="U8" s="81"/>
+      <c r="V8" s="84"/>
+      <c r="W8" s="84"/>
+      <c r="X8" s="11"/>
       <c r="Y8" s="5"/>
     </row>
-    <row r="9" spans="1:25" ht="18">
+    <row r="9" spans="1:25" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -1903,18 +1903,18 @@
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="12"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="11"/>
       <c r="Y9" s="5"/>
     </row>
-    <row r="10" spans="1:25" ht="18">
+    <row r="10" spans="1:25" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="85"/>
+      <c r="D10" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="13" t="s">
-        <v>13</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -1924,11 +1924,11 @@
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
       <c r="Y10" s="5"/>
     </row>
-    <row r="11" spans="1:25" ht="14.25">
+    <row r="11" spans="1:25" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -1947,1489 +1947,1588 @@
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
     </row>
-    <row r="12" spans="1:25" ht="16.5">
-      <c r="A12" s="14"/>
-      <c r="B12" s="59" t="s">
+    <row r="12" spans="1:25" ht="16" x14ac:dyDescent="0.3">
+      <c r="A12" s="13"/>
+      <c r="B12" s="86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="D12" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="63" t="s">
+      <c r="E12" s="90"/>
+      <c r="F12" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="64"/>
-      <c r="F12" s="67" t="s">
+      <c r="G12" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="59" t="s">
+      <c r="H12" s="89"/>
+      <c r="I12" s="89"/>
+      <c r="J12" s="89"/>
+      <c r="K12" s="89"/>
+      <c r="L12" s="89"/>
+      <c r="M12" s="89"/>
+      <c r="N12" s="95"/>
+      <c r="O12" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="63"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="69"/>
-      <c r="O12" s="70" t="s">
+      <c r="P12" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="P12" s="59" t="s">
+      <c r="Q12" s="98"/>
+      <c r="R12" s="99"/>
+      <c r="S12" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="73"/>
-      <c r="S12" s="74" t="s">
+      <c r="T12" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="T12" s="75" t="s">
+      <c r="U12" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="U12" s="76" t="s">
+      <c r="V12" s="72"/>
+      <c r="W12" s="72"/>
+      <c r="X12" s="72"/>
+    </row>
+    <row r="13" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="13"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="92"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="97"/>
+      <c r="P13" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="V12" s="76"/>
-      <c r="W12" s="76"/>
-      <c r="X12" s="76"/>
-    </row>
-    <row r="13" spans="1:25" ht="33" customHeight="1">
-      <c r="A13" s="14"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="78" t="s">
+      <c r="Q13" s="75"/>
+      <c r="R13" s="76"/>
+      <c r="S13" s="88"/>
+      <c r="T13" s="71"/>
+      <c r="U13" s="72"/>
+      <c r="V13" s="72"/>
+      <c r="W13" s="72"/>
+      <c r="X13" s="72"/>
+    </row>
+    <row r="14" spans="1:25" ht="16" x14ac:dyDescent="0.3">
+      <c r="A14" s="13"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="92"/>
+      <c r="F14" s="94"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="97"/>
+      <c r="P14" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="Q13" s="79"/>
-      <c r="R13" s="80"/>
-      <c r="S13" s="62"/>
-      <c r="T13" s="60"/>
-      <c r="U13" s="76"/>
-      <c r="V13" s="76"/>
-      <c r="W13" s="76"/>
-      <c r="X13" s="76"/>
-    </row>
-    <row r="14" spans="1:25" ht="16.5">
-      <c r="A14" s="14"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="20" t="s">
+      <c r="Q14" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="Q14" s="21" t="s">
+      <c r="R14" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="R14" s="22" t="s">
+      <c r="S14" s="88"/>
+      <c r="T14" s="71"/>
+      <c r="U14" s="73"/>
+      <c r="V14" s="73"/>
+      <c r="W14" s="73"/>
+      <c r="X14" s="73"/>
+    </row>
+    <row r="15" spans="1:25" s="27" customFormat="1" ht="16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="13"/>
+      <c r="B15" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="S14" s="62"/>
-      <c r="T14" s="60"/>
-      <c r="U14" s="77"/>
-      <c r="V14" s="77"/>
-      <c r="W14" s="77"/>
-      <c r="X14" s="77"/>
-    </row>
-    <row r="15" spans="1:25" s="28" customFormat="1" ht="16.5">
-      <c r="A15" s="14"/>
-      <c r="B15" s="91" t="s">
+      <c r="C15" s="64"/>
+      <c r="D15" s="65">
+        <f>COUNTA(D17:E57)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="66"/>
+      <c r="F15" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="92"/>
-      <c r="D15" s="93">
-        <f>COUNTA(D17:E57)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="94"/>
-      <c r="F15" s="23" t="s">
+      <c r="G15" s="55">
+        <f>COUNTIF(G17:G57,"〇")</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="55">
+        <f t="shared" ref="H15:N15" si="0">COUNTIF(H17:H57,"〇")</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="56">
+        <f>SUM(O17:O57)</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="67"/>
+      <c r="V15" s="68"/>
+      <c r="W15" s="68"/>
+      <c r="X15" s="68"/>
+    </row>
+    <row r="16" spans="1:25" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="56">
-        <f>COUNTIF(G17:G57,"〇")</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="56">
-        <f t="shared" ref="H15:N15" si="0">COUNTIF(H17:H57,"〇")</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="56">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="56">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="56"/>
-      <c r="L15" s="56"/>
-      <c r="M15" s="56"/>
-      <c r="N15" s="56">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="57">
-        <f>SUM(O17:O57)</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="27"/>
-      <c r="T15" s="27"/>
-      <c r="U15" s="95"/>
-      <c r="V15" s="96"/>
-      <c r="W15" s="96"/>
-      <c r="X15" s="96"/>
-    </row>
-    <row r="16" spans="1:25" ht="17.25">
-      <c r="A16" s="29"/>
-      <c r="B16" s="30" t="s">
+      <c r="C16" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="D16" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="97" t="s">
+      <c r="E16" s="58"/>
+      <c r="F16" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="98"/>
-      <c r="F16" s="32" t="s">
+      <c r="G16" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34" t="s">
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="35">
+        <v>2300</v>
+      </c>
+      <c r="P16" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="36">
-        <v>2300</v>
-      </c>
-      <c r="P16" s="37" t="s">
+      <c r="Q16" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="Q16" s="38" t="s">
+      <c r="R16" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="R16" s="32" t="s">
+      <c r="S16" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="S16" s="39" t="s">
+      <c r="T16" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="U16" s="69"/>
+      <c r="V16" s="69"/>
+      <c r="W16" s="69"/>
+      <c r="X16" s="69"/>
+    </row>
+    <row r="17" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="40">
+        <v>1</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="46">
+        <f t="shared" ref="O17:O57" si="1">SUMIFS($G$14:$J$14,G17:J17,"〇")</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="47"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="49"/>
+      <c r="S17" s="50"/>
+      <c r="T17" s="51"/>
+      <c r="U17" s="59"/>
+      <c r="V17" s="59"/>
+      <c r="W17" s="59"/>
+      <c r="X17" s="59"/>
+    </row>
+    <row r="18" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="40">
+        <v>2</v>
+      </c>
+      <c r="C18" s="41"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="47"/>
+      <c r="Q18" s="48"/>
+      <c r="R18" s="49"/>
+      <c r="S18" s="50"/>
+      <c r="T18" s="51"/>
+      <c r="U18" s="59"/>
+      <c r="V18" s="59"/>
+      <c r="W18" s="59"/>
+      <c r="X18" s="59"/>
+    </row>
+    <row r="19" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="40">
+        <v>3</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="45"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="52"/>
+      <c r="S19" s="53"/>
+      <c r="T19" s="54"/>
+      <c r="U19" s="59"/>
+      <c r="V19" s="59"/>
+      <c r="W19" s="59"/>
+      <c r="X19" s="59"/>
+    </row>
+    <row r="20" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="40">
+        <v>4</v>
+      </c>
+      <c r="C20" s="41"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="48"/>
+      <c r="R20" s="52"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="40"/>
+      <c r="U20" s="59"/>
+      <c r="V20" s="59"/>
+      <c r="W20" s="59"/>
+      <c r="X20" s="59"/>
+    </row>
+    <row r="21" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="40">
+        <v>5</v>
+      </c>
+      <c r="C21" s="41"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="45"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P21" s="47"/>
+      <c r="Q21" s="48"/>
+      <c r="R21" s="52"/>
+      <c r="S21" s="41"/>
+      <c r="T21" s="40"/>
+      <c r="U21" s="59"/>
+      <c r="V21" s="59"/>
+      <c r="W21" s="59"/>
+      <c r="X21" s="59"/>
+    </row>
+    <row r="22" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="40">
+        <v>6</v>
+      </c>
+      <c r="C22" s="41"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="45"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P22" s="47"/>
+      <c r="Q22" s="48"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="41"/>
+      <c r="T22" s="40"/>
+      <c r="U22" s="59"/>
+      <c r="V22" s="59"/>
+      <c r="W22" s="59"/>
+      <c r="X22" s="59"/>
+    </row>
+    <row r="23" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="40">
+        <v>7</v>
+      </c>
+      <c r="C23" s="41"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="47"/>
+      <c r="Q23" s="48"/>
+      <c r="R23" s="52"/>
+      <c r="S23" s="41"/>
+      <c r="T23" s="40"/>
+      <c r="U23" s="59"/>
+      <c r="V23" s="59"/>
+      <c r="W23" s="59"/>
+      <c r="X23" s="59"/>
+    </row>
+    <row r="24" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="B24" s="40">
+        <v>8</v>
+      </c>
+      <c r="C24" s="41"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="47"/>
+      <c r="Q24" s="48"/>
+      <c r="R24" s="52"/>
+      <c r="S24" s="41"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="59"/>
+      <c r="V24" s="59"/>
+      <c r="W24" s="59"/>
+      <c r="X24" s="59"/>
+    </row>
+    <row r="25" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="B25" s="40">
+        <v>9</v>
+      </c>
+      <c r="C25" s="41"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="47"/>
+      <c r="Q25" s="48"/>
+      <c r="R25" s="52"/>
+      <c r="S25" s="41"/>
+      <c r="T25" s="40"/>
+      <c r="U25" s="59"/>
+      <c r="V25" s="59"/>
+      <c r="W25" s="59"/>
+      <c r="X25" s="59"/>
+    </row>
+    <row r="26" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="B26" s="40">
+        <v>10</v>
+      </c>
+      <c r="C26" s="41"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="47"/>
+      <c r="Q26" s="48"/>
+      <c r="R26" s="52"/>
+      <c r="S26" s="41"/>
+      <c r="T26" s="40"/>
+      <c r="U26" s="59"/>
+      <c r="V26" s="59"/>
+      <c r="W26" s="59"/>
+      <c r="X26" s="59"/>
+    </row>
+    <row r="27" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+      <c r="B27" s="40">
+        <v>11</v>
+      </c>
+      <c r="C27" s="41"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="47"/>
+      <c r="Q27" s="48"/>
+      <c r="R27" s="52"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="40"/>
+      <c r="U27" s="59"/>
+      <c r="V27" s="59"/>
+      <c r="W27" s="59"/>
+      <c r="X27" s="59"/>
+    </row>
+    <row r="28" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+      <c r="B28" s="40">
+        <v>12</v>
+      </c>
+      <c r="C28" s="41"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="47"/>
+      <c r="Q28" s="48"/>
+      <c r="R28" s="52"/>
+      <c r="S28" s="41"/>
+      <c r="T28" s="40"/>
+      <c r="U28" s="59"/>
+      <c r="V28" s="59"/>
+      <c r="W28" s="59"/>
+      <c r="X28" s="59"/>
+    </row>
+    <row r="29" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="40">
+        <v>13</v>
+      </c>
+      <c r="C29" s="41"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P29" s="47"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="52"/>
+      <c r="S29" s="41"/>
+      <c r="T29" s="40"/>
+      <c r="U29" s="59"/>
+      <c r="V29" s="59"/>
+      <c r="W29" s="59"/>
+      <c r="X29" s="59"/>
+    </row>
+    <row r="30" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+      <c r="B30" s="40">
+        <v>14</v>
+      </c>
+      <c r="C30" s="41"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P30" s="47"/>
+      <c r="Q30" s="48"/>
+      <c r="R30" s="52"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="40"/>
+      <c r="U30" s="59"/>
+      <c r="V30" s="59"/>
+      <c r="W30" s="59"/>
+      <c r="X30" s="59"/>
+    </row>
+    <row r="31" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="5"/>
+      <c r="B31" s="40">
+        <v>15</v>
+      </c>
+      <c r="C31" s="41"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45"/>
+      <c r="M31" s="45"/>
+      <c r="N31" s="45"/>
+      <c r="O31" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="47"/>
+      <c r="Q31" s="48"/>
+      <c r="R31" s="52"/>
+      <c r="S31" s="41"/>
+      <c r="T31" s="40"/>
+      <c r="U31" s="59"/>
+      <c r="V31" s="59"/>
+      <c r="W31" s="59"/>
+      <c r="X31" s="59"/>
+    </row>
+    <row r="32" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="5"/>
+      <c r="B32" s="40">
+        <v>16</v>
+      </c>
+      <c r="C32" s="41"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="45"/>
+      <c r="N32" s="45"/>
+      <c r="O32" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P32" s="47"/>
+      <c r="Q32" s="48"/>
+      <c r="R32" s="52"/>
+      <c r="S32" s="41"/>
+      <c r="T32" s="40"/>
+      <c r="U32" s="59"/>
+      <c r="V32" s="59"/>
+      <c r="W32" s="59"/>
+      <c r="X32" s="59"/>
+    </row>
+    <row r="33" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="5"/>
+      <c r="B33" s="40">
+        <v>17</v>
+      </c>
+      <c r="C33" s="41"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="45"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P33" s="47"/>
+      <c r="Q33" s="48"/>
+      <c r="R33" s="52"/>
+      <c r="S33" s="41"/>
+      <c r="T33" s="40"/>
+      <c r="U33" s="59"/>
+      <c r="V33" s="59"/>
+      <c r="W33" s="59"/>
+      <c r="X33" s="59"/>
+    </row>
+    <row r="34" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="5"/>
+      <c r="B34" s="40">
+        <v>18</v>
+      </c>
+      <c r="C34" s="41"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="45"/>
+      <c r="M34" s="45"/>
+      <c r="N34" s="45"/>
+      <c r="O34" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P34" s="47"/>
+      <c r="Q34" s="48"/>
+      <c r="R34" s="52"/>
+      <c r="S34" s="41"/>
+      <c r="T34" s="40"/>
+      <c r="U34" s="59"/>
+      <c r="V34" s="59"/>
+      <c r="W34" s="59"/>
+      <c r="X34" s="59"/>
+    </row>
+    <row r="35" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="5"/>
+      <c r="B35" s="40">
+        <v>19</v>
+      </c>
+      <c r="C35" s="41"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="45"/>
+      <c r="M35" s="45"/>
+      <c r="N35" s="45"/>
+      <c r="O35" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="47"/>
+      <c r="Q35" s="48"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="41"/>
+      <c r="T35" s="40"/>
+      <c r="U35" s="59"/>
+      <c r="V35" s="59"/>
+      <c r="W35" s="59"/>
+      <c r="X35" s="59"/>
+    </row>
+    <row r="36" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="5"/>
+      <c r="B36" s="40">
+        <v>20</v>
+      </c>
+      <c r="C36" s="41"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="45"/>
+      <c r="M36" s="45"/>
+      <c r="N36" s="45"/>
+      <c r="O36" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P36" s="47"/>
+      <c r="Q36" s="48"/>
+      <c r="R36" s="52"/>
+      <c r="S36" s="41"/>
+      <c r="T36" s="40"/>
+      <c r="U36" s="59"/>
+      <c r="V36" s="59"/>
+      <c r="W36" s="59"/>
+      <c r="X36" s="59"/>
+    </row>
+    <row r="37" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="5"/>
+      <c r="B37" s="40">
+        <v>21</v>
+      </c>
+      <c r="C37" s="41"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="45"/>
+      <c r="M37" s="45"/>
+      <c r="N37" s="45"/>
+      <c r="O37" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P37" s="47"/>
+      <c r="Q37" s="48"/>
+      <c r="R37" s="52"/>
+      <c r="S37" s="41"/>
+      <c r="T37" s="40"/>
+      <c r="U37" s="59"/>
+      <c r="V37" s="59"/>
+      <c r="W37" s="59"/>
+      <c r="X37" s="59"/>
+    </row>
+    <row r="38" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="5"/>
+      <c r="B38" s="40">
+        <v>22</v>
+      </c>
+      <c r="C38" s="41"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="45"/>
+      <c r="M38" s="45"/>
+      <c r="N38" s="45"/>
+      <c r="O38" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P38" s="47"/>
+      <c r="Q38" s="48"/>
+      <c r="R38" s="52"/>
+      <c r="S38" s="41"/>
+      <c r="T38" s="40"/>
+      <c r="U38" s="59"/>
+      <c r="V38" s="59"/>
+      <c r="W38" s="59"/>
+      <c r="X38" s="59"/>
+    </row>
+    <row r="39" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="5"/>
+      <c r="B39" s="40">
+        <v>23</v>
+      </c>
+      <c r="C39" s="41"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
+      <c r="O39" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P39" s="47"/>
+      <c r="Q39" s="48"/>
+      <c r="R39" s="52"/>
+      <c r="S39" s="41"/>
+      <c r="T39" s="40"/>
+      <c r="U39" s="59"/>
+      <c r="V39" s="59"/>
+      <c r="W39" s="59"/>
+      <c r="X39" s="59"/>
+    </row>
+    <row r="40" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="5"/>
+      <c r="B40" s="40">
+        <v>24</v>
+      </c>
+      <c r="C40" s="41"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="45"/>
+      <c r="O40" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P40" s="47"/>
+      <c r="Q40" s="48"/>
+      <c r="R40" s="52"/>
+      <c r="S40" s="41"/>
+      <c r="T40" s="40"/>
+      <c r="U40" s="59"/>
+      <c r="V40" s="59"/>
+      <c r="W40" s="59"/>
+      <c r="X40" s="59"/>
+    </row>
+    <row r="41" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="5"/>
+      <c r="B41" s="40">
+        <v>25</v>
+      </c>
+      <c r="C41" s="41"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="44"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45"/>
+      <c r="M41" s="45"/>
+      <c r="N41" s="45"/>
+      <c r="O41" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P41" s="47"/>
+      <c r="Q41" s="48"/>
+      <c r="R41" s="52"/>
+      <c r="S41" s="41"/>
+      <c r="T41" s="40"/>
+      <c r="U41" s="59"/>
+      <c r="V41" s="59"/>
+      <c r="W41" s="59"/>
+      <c r="X41" s="59"/>
+    </row>
+    <row r="42" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="5"/>
+      <c r="B42" s="40">
+        <v>26</v>
+      </c>
+      <c r="C42" s="41"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="45"/>
+      <c r="O42" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P42" s="47"/>
+      <c r="Q42" s="48"/>
+      <c r="R42" s="52"/>
+      <c r="S42" s="41"/>
+      <c r="T42" s="40"/>
+      <c r="U42" s="59"/>
+      <c r="V42" s="59"/>
+      <c r="W42" s="59"/>
+      <c r="X42" s="59"/>
+    </row>
+    <row r="43" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="5"/>
+      <c r="B43" s="40">
+        <v>27</v>
+      </c>
+      <c r="C43" s="41"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="45"/>
+      <c r="L43" s="45"/>
+      <c r="M43" s="45"/>
+      <c r="N43" s="45"/>
+      <c r="O43" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P43" s="47"/>
+      <c r="Q43" s="48"/>
+      <c r="R43" s="52"/>
+      <c r="S43" s="41"/>
+      <c r="T43" s="40"/>
+      <c r="U43" s="59"/>
+      <c r="V43" s="59"/>
+      <c r="W43" s="59"/>
+      <c r="X43" s="59"/>
+    </row>
+    <row r="44" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="5"/>
+      <c r="B44" s="40">
+        <v>28</v>
+      </c>
+      <c r="C44" s="41"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="45"/>
+      <c r="L44" s="45"/>
+      <c r="M44" s="45"/>
+      <c r="N44" s="45"/>
+      <c r="O44" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P44" s="47"/>
+      <c r="Q44" s="48"/>
+      <c r="R44" s="52"/>
+      <c r="S44" s="41"/>
+      <c r="T44" s="40"/>
+      <c r="U44" s="59"/>
+      <c r="V44" s="59"/>
+      <c r="W44" s="59"/>
+      <c r="X44" s="59"/>
+    </row>
+    <row r="45" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="5"/>
+      <c r="B45" s="40">
+        <v>29</v>
+      </c>
+      <c r="C45" s="41"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="45"/>
+      <c r="M45" s="45"/>
+      <c r="N45" s="45"/>
+      <c r="O45" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P45" s="47"/>
+      <c r="Q45" s="48"/>
+      <c r="R45" s="52"/>
+      <c r="S45" s="41"/>
+      <c r="T45" s="40"/>
+      <c r="U45" s="59"/>
+      <c r="V45" s="59"/>
+      <c r="W45" s="59"/>
+      <c r="X45" s="59"/>
+    </row>
+    <row r="46" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="5"/>
+      <c r="B46" s="40">
+        <v>30</v>
+      </c>
+      <c r="C46" s="41"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="45"/>
+      <c r="M46" s="45"/>
+      <c r="N46" s="45"/>
+      <c r="O46" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P46" s="47"/>
+      <c r="Q46" s="48"/>
+      <c r="R46" s="52"/>
+      <c r="S46" s="41"/>
+      <c r="T46" s="40"/>
+      <c r="U46" s="59"/>
+      <c r="V46" s="59"/>
+      <c r="W46" s="59"/>
+      <c r="X46" s="59"/>
+    </row>
+    <row r="47" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="5"/>
+      <c r="B47" s="40">
+        <v>31</v>
+      </c>
+      <c r="C47" s="41"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="45"/>
+      <c r="M47" s="45"/>
+      <c r="N47" s="45"/>
+      <c r="O47" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P47" s="47"/>
+      <c r="Q47" s="48"/>
+      <c r="R47" s="52"/>
+      <c r="S47" s="41"/>
+      <c r="T47" s="40"/>
+      <c r="U47" s="59"/>
+      <c r="V47" s="59"/>
+      <c r="W47" s="59"/>
+      <c r="X47" s="59"/>
+    </row>
+    <row r="48" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="5"/>
+      <c r="B48" s="40">
+        <v>32</v>
+      </c>
+      <c r="C48" s="41"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="58"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="45"/>
+      <c r="M48" s="45"/>
+      <c r="N48" s="45"/>
+      <c r="O48" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P48" s="47"/>
+      <c r="Q48" s="48"/>
+      <c r="R48" s="52"/>
+      <c r="S48" s="41"/>
+      <c r="T48" s="40"/>
+      <c r="U48" s="59"/>
+      <c r="V48" s="59"/>
+      <c r="W48" s="59"/>
+      <c r="X48" s="59"/>
+    </row>
+    <row r="49" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="5"/>
+      <c r="B49" s="40">
+        <v>33</v>
+      </c>
+      <c r="C49" s="41"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="44"/>
+      <c r="J49" s="44"/>
+      <c r="K49" s="45"/>
+      <c r="L49" s="45"/>
+      <c r="M49" s="45"/>
+      <c r="N49" s="45"/>
+      <c r="O49" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P49" s="47"/>
+      <c r="Q49" s="48"/>
+      <c r="R49" s="52"/>
+      <c r="S49" s="41"/>
+      <c r="T49" s="40"/>
+      <c r="U49" s="59"/>
+      <c r="V49" s="59"/>
+      <c r="W49" s="59"/>
+      <c r="X49" s="59"/>
+    </row>
+    <row r="50" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="5"/>
+      <c r="B50" s="40">
+        <v>34</v>
+      </c>
+      <c r="C50" s="41"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="45"/>
+      <c r="M50" s="45"/>
+      <c r="N50" s="45"/>
+      <c r="O50" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P50" s="47"/>
+      <c r="Q50" s="48"/>
+      <c r="R50" s="52"/>
+      <c r="S50" s="41"/>
+      <c r="T50" s="40"/>
+      <c r="U50" s="59"/>
+      <c r="V50" s="59"/>
+      <c r="W50" s="59"/>
+      <c r="X50" s="59"/>
+    </row>
+    <row r="51" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="5"/>
+      <c r="B51" s="40">
+        <v>35</v>
+      </c>
+      <c r="C51" s="41"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="44"/>
+      <c r="J51" s="44"/>
+      <c r="K51" s="45"/>
+      <c r="L51" s="45"/>
+      <c r="M51" s="45"/>
+      <c r="N51" s="45"/>
+      <c r="O51" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P51" s="47"/>
+      <c r="Q51" s="48"/>
+      <c r="R51" s="52"/>
+      <c r="S51" s="41"/>
+      <c r="T51" s="40"/>
+      <c r="U51" s="59"/>
+      <c r="V51" s="59"/>
+      <c r="W51" s="59"/>
+      <c r="X51" s="59"/>
+    </row>
+    <row r="52" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="5"/>
+      <c r="B52" s="40">
+        <v>36</v>
+      </c>
+      <c r="C52" s="41"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="58"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="44"/>
+      <c r="J52" s="44"/>
+      <c r="K52" s="45"/>
+      <c r="L52" s="45"/>
+      <c r="M52" s="45"/>
+      <c r="N52" s="45"/>
+      <c r="O52" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P52" s="47"/>
+      <c r="Q52" s="48"/>
+      <c r="R52" s="52"/>
+      <c r="S52" s="41"/>
+      <c r="T52" s="40"/>
+      <c r="U52" s="59"/>
+      <c r="V52" s="59"/>
+      <c r="W52" s="59"/>
+      <c r="X52" s="59"/>
+    </row>
+    <row r="53" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="5"/>
+      <c r="B53" s="40">
+        <v>37</v>
+      </c>
+      <c r="C53" s="41"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="44"/>
+      <c r="J53" s="44"/>
+      <c r="K53" s="45"/>
+      <c r="L53" s="45"/>
+      <c r="M53" s="45"/>
+      <c r="N53" s="45"/>
+      <c r="O53" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P53" s="47"/>
+      <c r="Q53" s="48"/>
+      <c r="R53" s="52"/>
+      <c r="S53" s="41"/>
+      <c r="T53" s="40"/>
+      <c r="U53" s="59"/>
+      <c r="V53" s="59"/>
+      <c r="W53" s="59"/>
+      <c r="X53" s="59"/>
+    </row>
+    <row r="54" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="5"/>
+      <c r="B54" s="40">
+        <v>38</v>
+      </c>
+      <c r="C54" s="41"/>
+      <c r="D54" s="57"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="44"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="45"/>
+      <c r="M54" s="45"/>
+      <c r="N54" s="45"/>
+      <c r="O54" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P54" s="47"/>
+      <c r="Q54" s="48"/>
+      <c r="R54" s="52"/>
+      <c r="S54" s="41"/>
+      <c r="T54" s="40"/>
+      <c r="U54" s="59"/>
+      <c r="V54" s="59"/>
+      <c r="W54" s="59"/>
+      <c r="X54" s="59"/>
+    </row>
+    <row r="55" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="5"/>
+      <c r="B55" s="40">
         <v>39</v>
       </c>
-      <c r="T16" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="U16" s="99"/>
-      <c r="V16" s="99"/>
-      <c r="W16" s="99"/>
-      <c r="X16" s="99"/>
-    </row>
-    <row r="17" spans="1:24" ht="37.5" customHeight="1">
-      <c r="A17" s="5"/>
-      <c r="B17" s="41">
-        <v>1</v>
-      </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="47">
-        <f t="shared" ref="O17:O57" si="1">SUMIFS($G$14:$J$14,G17:J17,"〇")</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="49"/>
-      <c r="R17" s="50"/>
-      <c r="S17" s="51"/>
-      <c r="T17" s="52"/>
-      <c r="U17" s="90"/>
-      <c r="V17" s="90"/>
-      <c r="W17" s="90"/>
-      <c r="X17" s="90"/>
-    </row>
-    <row r="18" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A18" s="5"/>
-      <c r="B18" s="41">
-        <v>2</v>
-      </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="49"/>
-      <c r="R18" s="50"/>
-      <c r="S18" s="51"/>
-      <c r="T18" s="52"/>
-      <c r="U18" s="90"/>
-      <c r="V18" s="90"/>
-      <c r="W18" s="90"/>
-      <c r="X18" s="90"/>
-    </row>
-    <row r="19" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="41">
-        <v>3</v>
-      </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
-      <c r="O19" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="49"/>
-      <c r="R19" s="53"/>
-      <c r="S19" s="54"/>
-      <c r="T19" s="55"/>
-      <c r="U19" s="90"/>
-      <c r="V19" s="90"/>
-      <c r="W19" s="90"/>
-      <c r="X19" s="90"/>
-    </row>
-    <row r="20" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A20" s="5"/>
-      <c r="B20" s="41">
-        <v>4</v>
-      </c>
-      <c r="C20" s="42"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="46"/>
-      <c r="O20" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="49"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="90"/>
-      <c r="V20" s="90"/>
-      <c r="W20" s="90"/>
-      <c r="X20" s="90"/>
-    </row>
-    <row r="21" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A21" s="5"/>
-      <c r="B21" s="41">
-        <v>5</v>
-      </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
-      <c r="O21" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="49"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="42"/>
-      <c r="T21" s="41"/>
-      <c r="U21" s="90"/>
-      <c r="V21" s="90"/>
-      <c r="W21" s="90"/>
-      <c r="X21" s="90"/>
-    </row>
-    <row r="22" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="41">
-        <v>6</v>
-      </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46"/>
-      <c r="M22" s="46"/>
-      <c r="N22" s="46"/>
-      <c r="O22" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="49"/>
-      <c r="R22" s="53"/>
-      <c r="S22" s="42"/>
-      <c r="T22" s="41"/>
-      <c r="U22" s="90"/>
-      <c r="V22" s="90"/>
-      <c r="W22" s="90"/>
-      <c r="X22" s="90"/>
-    </row>
-    <row r="23" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="41">
-        <v>7</v>
-      </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="89"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="46"/>
-      <c r="N23" s="46"/>
-      <c r="O23" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="49"/>
-      <c r="R23" s="53"/>
-      <c r="S23" s="42"/>
-      <c r="T23" s="41"/>
-      <c r="U23" s="90"/>
-      <c r="V23" s="90"/>
-      <c r="W23" s="90"/>
-      <c r="X23" s="90"/>
-    </row>
-    <row r="24" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A24" s="5"/>
-      <c r="B24" s="41">
-        <v>8</v>
-      </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
-      <c r="O24" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="49"/>
-      <c r="R24" s="53"/>
-      <c r="S24" s="42"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="90"/>
-      <c r="V24" s="90"/>
-      <c r="W24" s="90"/>
-      <c r="X24" s="90"/>
-    </row>
-    <row r="25" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A25" s="5"/>
-      <c r="B25" s="41">
-        <v>9</v>
-      </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="89"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="49"/>
-      <c r="R25" s="53"/>
-      <c r="S25" s="42"/>
-      <c r="T25" s="41"/>
-      <c r="U25" s="90"/>
-      <c r="V25" s="90"/>
-      <c r="W25" s="90"/>
-      <c r="X25" s="90"/>
-    </row>
-    <row r="26" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A26" s="5"/>
-      <c r="B26" s="41">
-        <v>10</v>
-      </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
-      <c r="O26" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="53"/>
-      <c r="S26" s="42"/>
-      <c r="T26" s="41"/>
-      <c r="U26" s="90"/>
-      <c r="V26" s="90"/>
-      <c r="W26" s="90"/>
-      <c r="X26" s="90"/>
-    </row>
-    <row r="27" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A27" s="5"/>
-      <c r="B27" s="41">
-        <v>11</v>
-      </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
-      <c r="O27" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="49"/>
-      <c r="R27" s="53"/>
-      <c r="S27" s="42"/>
-      <c r="T27" s="41"/>
-      <c r="U27" s="90"/>
-      <c r="V27" s="90"/>
-      <c r="W27" s="90"/>
-      <c r="X27" s="90"/>
-    </row>
-    <row r="28" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A28" s="5"/>
-      <c r="B28" s="41">
-        <v>12</v>
-      </c>
-      <c r="C28" s="42"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="46"/>
-      <c r="O28" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="42"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="90"/>
-      <c r="V28" s="90"/>
-      <c r="W28" s="90"/>
-      <c r="X28" s="90"/>
-    </row>
-    <row r="29" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A29" s="5"/>
-      <c r="B29" s="41">
-        <v>13</v>
-      </c>
-      <c r="C29" s="42"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="46"/>
-      <c r="N29" s="46"/>
-      <c r="O29" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="49"/>
-      <c r="R29" s="53"/>
-      <c r="S29" s="42"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="90"/>
-      <c r="V29" s="90"/>
-      <c r="W29" s="90"/>
-      <c r="X29" s="90"/>
-    </row>
-    <row r="30" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A30" s="5"/>
-      <c r="B30" s="41">
-        <v>14</v>
-      </c>
-      <c r="C30" s="42"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="101"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
-      <c r="O30" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="49"/>
-      <c r="R30" s="53"/>
-      <c r="S30" s="42"/>
-      <c r="T30" s="41"/>
-      <c r="U30" s="90"/>
-      <c r="V30" s="90"/>
-      <c r="W30" s="90"/>
-      <c r="X30" s="90"/>
-    </row>
-    <row r="31" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A31" s="5"/>
-      <c r="B31" s="41">
-        <v>15</v>
-      </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="46"/>
-      <c r="O31" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="49"/>
-      <c r="R31" s="53"/>
-      <c r="S31" s="42"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="90"/>
-      <c r="V31" s="90"/>
-      <c r="W31" s="90"/>
-      <c r="X31" s="90"/>
-    </row>
-    <row r="32" spans="1:24" ht="32.25" customHeight="1">
-      <c r="A32" s="5"/>
-      <c r="B32" s="41">
-        <v>16</v>
-      </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="100"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="46"/>
-      <c r="M32" s="46"/>
-      <c r="N32" s="46"/>
-      <c r="O32" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="49"/>
-      <c r="R32" s="53"/>
-      <c r="S32" s="42"/>
-      <c r="T32" s="41"/>
-      <c r="U32" s="90"/>
-      <c r="V32" s="90"/>
-      <c r="W32" s="90"/>
-      <c r="X32" s="90"/>
-    </row>
-    <row r="33" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A33" s="5"/>
-      <c r="B33" s="41">
-        <v>17</v>
-      </c>
-      <c r="C33" s="42"/>
-      <c r="D33" s="100"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="46"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46"/>
-      <c r="O33" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="49"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="42"/>
-      <c r="T33" s="41"/>
-      <c r="U33" s="90"/>
-      <c r="V33" s="90"/>
-      <c r="W33" s="90"/>
-      <c r="X33" s="90"/>
-    </row>
-    <row r="34" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A34" s="5"/>
-      <c r="B34" s="41">
-        <v>18</v>
-      </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
-      <c r="O34" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P34" s="48"/>
-      <c r="Q34" s="49"/>
-      <c r="R34" s="53"/>
-      <c r="S34" s="42"/>
-      <c r="T34" s="41"/>
-      <c r="U34" s="90"/>
-      <c r="V34" s="90"/>
-      <c r="W34" s="90"/>
-      <c r="X34" s="90"/>
-    </row>
-    <row r="35" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A35" s="5"/>
-      <c r="B35" s="41">
-        <v>19</v>
-      </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="100"/>
-      <c r="E35" s="98"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="45"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
-      <c r="O35" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P35" s="48"/>
-      <c r="Q35" s="49"/>
-      <c r="R35" s="53"/>
-      <c r="S35" s="42"/>
-      <c r="T35" s="41"/>
-      <c r="U35" s="90"/>
-      <c r="V35" s="90"/>
-      <c r="W35" s="90"/>
-      <c r="X35" s="90"/>
-    </row>
-    <row r="36" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A36" s="5"/>
-      <c r="B36" s="41">
-        <v>20</v>
-      </c>
-      <c r="C36" s="42"/>
-      <c r="D36" s="100"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="44"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="45"/>
-      <c r="K36" s="46"/>
-      <c r="L36" s="46"/>
-      <c r="M36" s="46"/>
-      <c r="N36" s="46"/>
-      <c r="O36" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P36" s="48"/>
-      <c r="Q36" s="49"/>
-      <c r="R36" s="53"/>
-      <c r="S36" s="42"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="90"/>
-      <c r="V36" s="90"/>
-      <c r="W36" s="90"/>
-      <c r="X36" s="90"/>
-    </row>
-    <row r="37" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A37" s="5"/>
-      <c r="B37" s="41">
-        <v>21</v>
-      </c>
-      <c r="C37" s="42"/>
-      <c r="D37" s="100"/>
-      <c r="E37" s="98"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="44"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="45"/>
-      <c r="K37" s="46"/>
-      <c r="L37" s="46"/>
-      <c r="M37" s="46"/>
-      <c r="N37" s="46"/>
-      <c r="O37" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P37" s="48"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="42"/>
-      <c r="T37" s="41"/>
-      <c r="U37" s="90"/>
-      <c r="V37" s="90"/>
-      <c r="W37" s="90"/>
-      <c r="X37" s="90"/>
-    </row>
-    <row r="38" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A38" s="5"/>
-      <c r="B38" s="41">
-        <v>22</v>
-      </c>
-      <c r="C38" s="42"/>
-      <c r="D38" s="100"/>
-      <c r="E38" s="98"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="45"/>
-      <c r="K38" s="46"/>
-      <c r="L38" s="46"/>
-      <c r="M38" s="46"/>
-      <c r="N38" s="46"/>
-      <c r="O38" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P38" s="48"/>
-      <c r="Q38" s="49"/>
-      <c r="R38" s="53"/>
-      <c r="S38" s="42"/>
-      <c r="T38" s="41"/>
-      <c r="U38" s="90"/>
-      <c r="V38" s="90"/>
-      <c r="W38" s="90"/>
-      <c r="X38" s="90"/>
-    </row>
-    <row r="39" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A39" s="5"/>
-      <c r="B39" s="41">
-        <v>23</v>
-      </c>
-      <c r="C39" s="42"/>
-      <c r="D39" s="100"/>
-      <c r="E39" s="98"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="45"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="46"/>
-      <c r="M39" s="46"/>
-      <c r="N39" s="46"/>
-      <c r="O39" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P39" s="48"/>
-      <c r="Q39" s="49"/>
-      <c r="R39" s="53"/>
-      <c r="S39" s="42"/>
-      <c r="T39" s="41"/>
-      <c r="U39" s="90"/>
-      <c r="V39" s="90"/>
-      <c r="W39" s="90"/>
-      <c r="X39" s="90"/>
-    </row>
-    <row r="40" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A40" s="5"/>
-      <c r="B40" s="41">
-        <v>24</v>
-      </c>
-      <c r="C40" s="42"/>
-      <c r="D40" s="97"/>
-      <c r="E40" s="98"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="46"/>
-      <c r="L40" s="46"/>
-      <c r="M40" s="46"/>
-      <c r="N40" s="46"/>
-      <c r="O40" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P40" s="48"/>
-      <c r="Q40" s="49"/>
-      <c r="R40" s="53"/>
-      <c r="S40" s="42"/>
-      <c r="T40" s="41"/>
-      <c r="U40" s="90"/>
-      <c r="V40" s="90"/>
-      <c r="W40" s="90"/>
-      <c r="X40" s="90"/>
-    </row>
-    <row r="41" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A41" s="5"/>
-      <c r="B41" s="41">
-        <v>25</v>
-      </c>
-      <c r="C41" s="42"/>
-      <c r="D41" s="97"/>
-      <c r="E41" s="98"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="45"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="45"/>
-      <c r="K41" s="46"/>
-      <c r="L41" s="46"/>
-      <c r="M41" s="46"/>
-      <c r="N41" s="46"/>
-      <c r="O41" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P41" s="48"/>
-      <c r="Q41" s="49"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="42"/>
-      <c r="T41" s="41"/>
-      <c r="U41" s="90"/>
-      <c r="V41" s="90"/>
-      <c r="W41" s="90"/>
-      <c r="X41" s="90"/>
-    </row>
-    <row r="42" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A42" s="5"/>
-      <c r="B42" s="41">
-        <v>26</v>
-      </c>
-      <c r="C42" s="42"/>
-      <c r="D42" s="97"/>
-      <c r="E42" s="98"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="45"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="45"/>
-      <c r="K42" s="46"/>
-      <c r="L42" s="46"/>
-      <c r="M42" s="46"/>
-      <c r="N42" s="46"/>
-      <c r="O42" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P42" s="48"/>
-      <c r="Q42" s="49"/>
-      <c r="R42" s="53"/>
-      <c r="S42" s="42"/>
-      <c r="T42" s="41"/>
-      <c r="U42" s="90"/>
-      <c r="V42" s="90"/>
-      <c r="W42" s="90"/>
-      <c r="X42" s="90"/>
-    </row>
-    <row r="43" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A43" s="5"/>
-      <c r="B43" s="41">
-        <v>27</v>
-      </c>
-      <c r="C43" s="42"/>
-      <c r="D43" s="97"/>
-      <c r="E43" s="98"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="45"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="45"/>
-      <c r="K43" s="46"/>
-      <c r="L43" s="46"/>
-      <c r="M43" s="46"/>
-      <c r="N43" s="46"/>
-      <c r="O43" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P43" s="48"/>
-      <c r="Q43" s="49"/>
-      <c r="R43" s="53"/>
-      <c r="S43" s="42"/>
-      <c r="T43" s="41"/>
-      <c r="U43" s="90"/>
-      <c r="V43" s="90"/>
-      <c r="W43" s="90"/>
-      <c r="X43" s="90"/>
-    </row>
-    <row r="44" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A44" s="5"/>
-      <c r="B44" s="41">
-        <v>28</v>
-      </c>
-      <c r="C44" s="42"/>
-      <c r="D44" s="97"/>
-      <c r="E44" s="98"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="45"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="46"/>
-      <c r="M44" s="46"/>
-      <c r="N44" s="46"/>
-      <c r="O44" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P44" s="48"/>
-      <c r="Q44" s="49"/>
-      <c r="R44" s="53"/>
-      <c r="S44" s="42"/>
-      <c r="T44" s="41"/>
-      <c r="U44" s="90"/>
-      <c r="V44" s="90"/>
-      <c r="W44" s="90"/>
-      <c r="X44" s="90"/>
-    </row>
-    <row r="45" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A45" s="5"/>
-      <c r="B45" s="41">
-        <v>29</v>
-      </c>
-      <c r="C45" s="42"/>
-      <c r="D45" s="97"/>
-      <c r="E45" s="98"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="45"/>
-      <c r="K45" s="46"/>
-      <c r="L45" s="46"/>
-      <c r="M45" s="46"/>
-      <c r="N45" s="46"/>
-      <c r="O45" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="49"/>
-      <c r="R45" s="53"/>
-      <c r="S45" s="42"/>
-      <c r="T45" s="41"/>
-      <c r="U45" s="90"/>
-      <c r="V45" s="90"/>
-      <c r="W45" s="90"/>
-      <c r="X45" s="90"/>
-    </row>
-    <row r="46" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A46" s="5"/>
-      <c r="B46" s="41">
-        <v>30</v>
-      </c>
-      <c r="C46" s="42"/>
-      <c r="D46" s="97"/>
-      <c r="E46" s="98"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="45"/>
-      <c r="K46" s="46"/>
-      <c r="L46" s="46"/>
-      <c r="M46" s="46"/>
-      <c r="N46" s="46"/>
-      <c r="O46" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P46" s="48"/>
-      <c r="Q46" s="49"/>
-      <c r="R46" s="53"/>
-      <c r="S46" s="42"/>
-      <c r="T46" s="41"/>
-      <c r="U46" s="90"/>
-      <c r="V46" s="90"/>
-      <c r="W46" s="90"/>
-      <c r="X46" s="90"/>
-    </row>
-    <row r="47" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A47" s="5"/>
-      <c r="B47" s="41">
-        <v>31</v>
-      </c>
-      <c r="C47" s="42"/>
-      <c r="D47" s="97"/>
-      <c r="E47" s="98"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="45"/>
-      <c r="K47" s="46"/>
-      <c r="L47" s="46"/>
-      <c r="M47" s="46"/>
-      <c r="N47" s="46"/>
-      <c r="O47" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P47" s="48"/>
-      <c r="Q47" s="49"/>
-      <c r="R47" s="53"/>
-      <c r="S47" s="42"/>
-      <c r="T47" s="41"/>
-      <c r="U47" s="90"/>
-      <c r="V47" s="90"/>
-      <c r="W47" s="90"/>
-      <c r="X47" s="90"/>
-    </row>
-    <row r="48" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A48" s="5"/>
-      <c r="B48" s="41">
-        <v>32</v>
-      </c>
-      <c r="C48" s="42"/>
-      <c r="D48" s="97"/>
-      <c r="E48" s="98"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="46"/>
-      <c r="L48" s="46"/>
-      <c r="M48" s="46"/>
-      <c r="N48" s="46"/>
-      <c r="O48" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P48" s="48"/>
-      <c r="Q48" s="49"/>
-      <c r="R48" s="53"/>
-      <c r="S48" s="42"/>
-      <c r="T48" s="41"/>
-      <c r="U48" s="90"/>
-      <c r="V48" s="90"/>
-      <c r="W48" s="90"/>
-      <c r="X48" s="90"/>
-    </row>
-    <row r="49" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A49" s="5"/>
-      <c r="B49" s="41">
-        <v>33</v>
-      </c>
-      <c r="C49" s="42"/>
-      <c r="D49" s="97"/>
-      <c r="E49" s="98"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="44"/>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45"/>
-      <c r="J49" s="45"/>
-      <c r="K49" s="46"/>
-      <c r="L49" s="46"/>
-      <c r="M49" s="46"/>
-      <c r="N49" s="46"/>
-      <c r="O49" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P49" s="48"/>
-      <c r="Q49" s="49"/>
-      <c r="R49" s="53"/>
-      <c r="S49" s="42"/>
-      <c r="T49" s="41"/>
-      <c r="U49" s="90"/>
-      <c r="V49" s="90"/>
-      <c r="W49" s="90"/>
-      <c r="X49" s="90"/>
-    </row>
-    <row r="50" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A50" s="5"/>
-      <c r="B50" s="41">
-        <v>34</v>
-      </c>
-      <c r="C50" s="42"/>
-      <c r="D50" s="97"/>
-      <c r="E50" s="98"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45"/>
-      <c r="K50" s="46"/>
-      <c r="L50" s="46"/>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
-      <c r="O50" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="49"/>
-      <c r="R50" s="53"/>
-      <c r="S50" s="42"/>
-      <c r="T50" s="41"/>
-      <c r="U50" s="90"/>
-      <c r="V50" s="90"/>
-      <c r="W50" s="90"/>
-      <c r="X50" s="90"/>
-    </row>
-    <row r="51" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A51" s="5"/>
-      <c r="B51" s="41">
-        <v>35</v>
-      </c>
-      <c r="C51" s="42"/>
-      <c r="D51" s="97"/>
-      <c r="E51" s="98"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="44"/>
-      <c r="H51" s="45"/>
-      <c r="I51" s="45"/>
-      <c r="J51" s="45"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46"/>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
-      <c r="O51" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="49"/>
-      <c r="R51" s="53"/>
-      <c r="S51" s="42"/>
-      <c r="T51" s="41"/>
-      <c r="U51" s="90"/>
-      <c r="V51" s="90"/>
-      <c r="W51" s="90"/>
-      <c r="X51" s="90"/>
-    </row>
-    <row r="52" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A52" s="5"/>
-      <c r="B52" s="41">
-        <v>36</v>
-      </c>
-      <c r="C52" s="42"/>
-      <c r="D52" s="97"/>
-      <c r="E52" s="98"/>
-      <c r="F52" s="43"/>
-      <c r="G52" s="44"/>
-      <c r="H52" s="45"/>
-      <c r="I52" s="45"/>
-      <c r="J52" s="45"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="46"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
-      <c r="O52" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P52" s="48"/>
-      <c r="Q52" s="49"/>
-      <c r="R52" s="53"/>
-      <c r="S52" s="42"/>
-      <c r="T52" s="41"/>
-      <c r="U52" s="90"/>
-      <c r="V52" s="90"/>
-      <c r="W52" s="90"/>
-      <c r="X52" s="90"/>
-    </row>
-    <row r="53" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A53" s="5"/>
-      <c r="B53" s="41">
-        <v>37</v>
-      </c>
-      <c r="C53" s="42"/>
-      <c r="D53" s="97"/>
-      <c r="E53" s="98"/>
-      <c r="F53" s="43"/>
-      <c r="G53" s="44"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="45"/>
-      <c r="K53" s="46"/>
-      <c r="L53" s="46"/>
-      <c r="M53" s="46"/>
-      <c r="N53" s="46"/>
-      <c r="O53" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P53" s="48"/>
-      <c r="Q53" s="49"/>
-      <c r="R53" s="53"/>
-      <c r="S53" s="42"/>
-      <c r="T53" s="41"/>
-      <c r="U53" s="90"/>
-      <c r="V53" s="90"/>
-      <c r="W53" s="90"/>
-      <c r="X53" s="90"/>
-    </row>
-    <row r="54" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A54" s="5"/>
-      <c r="B54" s="41">
-        <v>38</v>
-      </c>
-      <c r="C54" s="42"/>
-      <c r="D54" s="97"/>
-      <c r="E54" s="98"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="44"/>
-      <c r="H54" s="45"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="45"/>
-      <c r="K54" s="46"/>
-      <c r="L54" s="46"/>
-      <c r="M54" s="46"/>
-      <c r="N54" s="46"/>
-      <c r="O54" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P54" s="48"/>
-      <c r="Q54" s="49"/>
-      <c r="R54" s="53"/>
-      <c r="S54" s="42"/>
-      <c r="T54" s="41"/>
-      <c r="U54" s="90"/>
-      <c r="V54" s="90"/>
-      <c r="W54" s="90"/>
-      <c r="X54" s="90"/>
-    </row>
-    <row r="55" spans="1:24" ht="35.25" customHeight="1">
-      <c r="A55" s="5"/>
-      <c r="B55" s="41">
-        <v>39</v>
-      </c>
-      <c r="C55" s="42"/>
-      <c r="D55" s="97"/>
-      <c r="E55" s="98"/>
-      <c r="F55" s="43"/>
-      <c r="G55" s="44"/>
-      <c r="H55" s="45"/>
-      <c r="I55" s="45"/>
-      <c r="J55" s="45"/>
-      <c r="K55" s="46"/>
-      <c r="L55" s="46"/>
-      <c r="M55" s="46"/>
-      <c r="N55" s="46"/>
-      <c r="O55" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P55" s="48"/>
-      <c r="Q55" s="49"/>
-      <c r="R55" s="53"/>
-      <c r="S55" s="42"/>
-      <c r="T55" s="41"/>
-      <c r="U55" s="90"/>
-      <c r="V55" s="90"/>
-      <c r="W55" s="90"/>
-      <c r="X55" s="90"/>
-    </row>
-    <row r="56" spans="1:24" ht="35.25" customHeight="1">
+      <c r="C55" s="41"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="58"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="44"/>
+      <c r="J55" s="44"/>
+      <c r="K55" s="45"/>
+      <c r="L55" s="45"/>
+      <c r="M55" s="45"/>
+      <c r="N55" s="45"/>
+      <c r="O55" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P55" s="47"/>
+      <c r="Q55" s="48"/>
+      <c r="R55" s="52"/>
+      <c r="S55" s="41"/>
+      <c r="T55" s="40"/>
+      <c r="U55" s="59"/>
+      <c r="V55" s="59"/>
+      <c r="W55" s="59"/>
+      <c r="X55" s="59"/>
+    </row>
+    <row r="56" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
-      <c r="B56" s="41">
+      <c r="B56" s="40">
         <v>40</v>
       </c>
-      <c r="C56" s="42"/>
-      <c r="D56" s="97"/>
-      <c r="E56" s="98"/>
-      <c r="F56" s="43"/>
-      <c r="G56" s="44"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="45"/>
-      <c r="K56" s="46"/>
-      <c r="L56" s="46"/>
-      <c r="M56" s="46"/>
-      <c r="N56" s="46"/>
-      <c r="O56" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P56" s="48"/>
-      <c r="Q56" s="49"/>
-      <c r="R56" s="53"/>
-      <c r="S56" s="42"/>
-      <c r="T56" s="41"/>
-      <c r="U56" s="90"/>
-      <c r="V56" s="90"/>
-      <c r="W56" s="90"/>
-      <c r="X56" s="90"/>
-    </row>
-    <row r="57" spans="1:24" ht="35.25" customHeight="1">
+      <c r="C56" s="41"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="58"/>
+      <c r="F56" s="42"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="44"/>
+      <c r="J56" s="44"/>
+      <c r="K56" s="45"/>
+      <c r="L56" s="45"/>
+      <c r="M56" s="45"/>
+      <c r="N56" s="45"/>
+      <c r="O56" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P56" s="47"/>
+      <c r="Q56" s="48"/>
+      <c r="R56" s="52"/>
+      <c r="S56" s="41"/>
+      <c r="T56" s="40"/>
+      <c r="U56" s="59"/>
+      <c r="V56" s="59"/>
+      <c r="W56" s="59"/>
+      <c r="X56" s="59"/>
+    </row>
+    <row r="57" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
-      <c r="B57" s="41">
+      <c r="B57" s="40">
         <v>41</v>
       </c>
-      <c r="C57" s="42"/>
-      <c r="D57" s="97"/>
-      <c r="E57" s="98"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="44"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45"/>
-      <c r="J57" s="45"/>
-      <c r="K57" s="46"/>
-      <c r="L57" s="46"/>
-      <c r="M57" s="46"/>
-      <c r="N57" s="46"/>
-      <c r="O57" s="47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P57" s="48"/>
-      <c r="Q57" s="49"/>
-      <c r="R57" s="53"/>
-      <c r="S57" s="42"/>
-      <c r="T57" s="41"/>
-      <c r="U57" s="90"/>
-      <c r="V57" s="90"/>
-      <c r="W57" s="90"/>
-      <c r="X57" s="90"/>
+      <c r="C57" s="41"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="58"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="43"/>
+      <c r="H57" s="44"/>
+      <c r="I57" s="44"/>
+      <c r="J57" s="44"/>
+      <c r="K57" s="45"/>
+      <c r="L57" s="45"/>
+      <c r="M57" s="45"/>
+      <c r="N57" s="45"/>
+      <c r="O57" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P57" s="47"/>
+      <c r="Q57" s="48"/>
+      <c r="R57" s="52"/>
+      <c r="S57" s="41"/>
+      <c r="T57" s="40"/>
+      <c r="U57" s="59"/>
+      <c r="V57" s="59"/>
+      <c r="W57" s="59"/>
+      <c r="X57" s="59"/>
     </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="G17:N57" name="範囲1"/>
   </protectedRanges>
-  <mergeCells count="103">
+  <mergeCells count="104">
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="G12:N12"/>
+    <mergeCell ref="O12:O14"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="S12:S14"/>
+    <mergeCell ref="T12:T14"/>
+    <mergeCell ref="U12:X14"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="U5:U8"/>
+    <mergeCell ref="V5:V8"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="W5:W8"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="U20:X20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="U15:X15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="U16:X16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="U17:X17"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="U22:X22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="U36:X36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="U37:X37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="U38:X38"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="U35:X35"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="U44:X44"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="U39:X39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="U40:X40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="U41:X41"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="U48:X48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="U49:X49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="U50:X50"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="U45:X45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="U46:X46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="U47:X47"/>
     <mergeCell ref="D57:E57"/>
     <mergeCell ref="U57:X57"/>
     <mergeCell ref="D54:E54"/>
@@ -3444,95 +3543,6 @@
     <mergeCell ref="U52:X52"/>
     <mergeCell ref="D53:E53"/>
     <mergeCell ref="U53:X53"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="U48:X48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="U49:X49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="U50:X50"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="U45:X45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="U46:X46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="U47:X47"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="U42:X42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="U44:X44"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="U39:X39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="U40:X40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="U41:X41"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="U36:X36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="U37:X37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="U38:X38"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="U35:X35"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="U30:X30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="U31:X31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="U28:X28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="U29:X29"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="U25:X25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="U26:X26"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="U21:X21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="U22:X22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="U20:X20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="U15:X15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="U16:X16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="U17:X17"/>
-    <mergeCell ref="T12:T14"/>
-    <mergeCell ref="U12:X14"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="U5:U8"/>
-    <mergeCell ref="V5:V8"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:E14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="G12:N12"/>
-    <mergeCell ref="O12:O14"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="S12:S14"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <dataValidations count="1">
@@ -3738,15 +3748,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="e07dd695-b70d-4177-bfc3-4750b24c049d">
@@ -3757,14 +3758,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68A3CAA4-EE4A-4219-966B-E5F99A3E7686}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68A3CAA4-EE4A-4219-966B-E5F99A3E7686}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e07dd695-b70d-4177-bfc3-4750b24c049d"/>
+    <ds:schemaRef ds:uri="afd4e677-d9f8-4eb2-a5b6-468f89fa9c12"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4225371B-6968-4EF1-95FB-8B295058719D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7FF13C7-570C-4CB6-92D1-119C68B216B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e07dd695-b70d-4177-bfc3-4750b24c049d"/>
+    <ds:schemaRef ds:uri="afd4e677-d9f8-4eb2-a5b6-468f89fa9c12"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7FF13C7-570C-4CB6-92D1-119C68B216B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4225371B-6968-4EF1-95FB-8B295058719D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>